--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Lu 2006.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Lu 2006.xlsx
@@ -2146,7 +2146,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>2) Параметры алгоритма</t>
+          <t>2) Гиперпараметры алгоритма</t>
         </is>
       </c>
       <c r="B10" s="15" t="n"/>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Lu 2006.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Lu 2006.xlsx
@@ -2146,7 +2146,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>2) Гиперпараметры алгоритма</t>
+          <t>2) Параметры модели</t>
         </is>
       </c>
       <c r="B10" s="15" t="n"/>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Lu 2006.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Lu 2006.xlsx
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="B11" s="17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1"/>
@@ -3867,7 +3867,7 @@
         <v>1</v>
       </c>
       <c r="C111" s="17" t="n">
-        <v>0.8361799816345278</v>
+        <v>0.8255280073461899</v>
       </c>
       <c r="D111" s="17" t="n">
         <v>0</v>
@@ -3880,13 +3880,13 @@
         </is>
       </c>
       <c r="B112" s="17" t="n">
-        <v>0.8361799816345278</v>
+        <v>0.8255280073461899</v>
       </c>
       <c r="C112" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D112" s="17" t="n">
-        <v>0.07860422405876913</v>
+        <v>0.06795224977043124</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -3899,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="C113" s="17" t="n">
-        <v>0.07860422405876913</v>
+        <v>0.06795224977043124</v>
       </c>
       <c r="D113" s="17" t="n">
         <v>1</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="17" t="n">
-        <v>0.8361799816345272</v>
+        <v>0.8255280073461893</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -3960,7 +3960,7 @@
         <v>1</v>
       </c>
       <c r="D119" s="17" t="n">
-        <v>0.07860422405876943</v>
+        <v>0.06795224977043152</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="B120" s="17" t="n">
-        <v>0.8361799816345272</v>
+        <v>0.8255280073461893</v>
       </c>
       <c r="C120" s="17" t="n">
-        <v>0.07860422405876943</v>
+        <v>0.06795224977043152</v>
       </c>
       <c r="D120" s="17" t="n">
         <v>1</v>
@@ -4015,10 +4015,10 @@
         <v>1</v>
       </c>
       <c r="C125" s="17" t="n">
-        <v>0.8893814878892738</v>
+        <v>0.8819474480968863</v>
       </c>
       <c r="D125" s="17" t="n">
-        <v>0.05114619377162603</v>
+        <v>0.04371215397923852</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="B126" s="17" t="n">
-        <v>0.8893814878892738</v>
+        <v>0.8819474480968863</v>
       </c>
       <c r="C126" s="17" t="n">
         <v>1</v>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="B127" s="17" t="n">
-        <v>0.05114619377162603</v>
+        <v>0.04371215397923852</v>
       </c>
       <c r="C127" s="17" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="D132" s="17" t="n">
-        <v>0.7086419753086435</v>
+        <v>0.6913580246913595</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -4108,7 +4108,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="17" t="n">
-        <v>0.1530864197530855</v>
+        <v>0.1358024691358016</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="B134" s="17" t="n">
-        <v>0.7086419753086435</v>
+        <v>0.6913580246913595</v>
       </c>
       <c r="C134" s="17" t="n">
-        <v>0.1530864197530855</v>
+        <v>0.1358024691358016</v>
       </c>
       <c r="D134" s="17" t="n">
         <v>1</v>
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="B175" s="17" t="n">
-        <v>0.5508539944903583</v>
+        <v>0.547658402203857</v>
       </c>
       <c r="C175" s="17" t="n">
-        <v>0.582295684113866</v>
+        <v>0.5748393021120295</v>
       </c>
       <c r="D175" s="17" t="n">
-        <v>0.4235812672176308</v>
+        <v>0.4203856749311294</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -4570,13 +4570,13 @@
         </is>
       </c>
       <c r="B176" s="17" t="n">
-        <v>0.6344719926538109</v>
+        <v>0.6302112029384757</v>
       </c>
       <c r="C176" s="17" t="n">
-        <v>0.3314416896235078</v>
+        <v>0.3271808999081726</v>
       </c>
       <c r="D176" s="17" t="n">
-        <v>0.674435261707989</v>
+        <v>0.6680440771349863</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>0.5872729238754325</v>
+        <v>0.5820690960207613</v>
       </c>
       <c r="C177" s="17" t="n">
-        <v>0.5668144463667821</v>
+        <v>0.5645842344290659</v>
       </c>
       <c r="D177" s="17" t="n">
-        <v>0.4153438581314878</v>
+        <v>0.4131136461937716</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="B178" s="17" t="n">
-        <v>0.5834567901234574</v>
+        <v>0.5765432098765438</v>
       </c>
       <c r="C178" s="17" t="n">
-        <v>0.3612345679012341</v>
+        <v>0.3543209876543206</v>
       </c>
       <c r="D178" s="17" t="n">
-        <v>0.6585185185185187</v>
+        <v>0.6481481481481484</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -4748,13 +4748,13 @@
         </is>
       </c>
       <c r="B189" s="17" t="n">
-        <v>0.3538530508234629</v>
+        <v>0.3549577431258184</v>
       </c>
       <c r="C189" s="17" t="n">
-        <v>0.3740503043744987</v>
+        <v>0.3725746934888703</v>
       </c>
       <c r="D189" s="17" t="n">
-        <v>0.2720966448020385</v>
+        <v>0.2724675633853111</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>0.3867908684796848</v>
+        <v>0.3877182080108468</v>
       </c>
       <c r="C190" s="17" t="n">
-        <v>0.2020555997178589</v>
+        <v>0.2012880628213095</v>
       </c>
       <c r="D190" s="17" t="n">
-        <v>0.4111535318024564</v>
+        <v>0.4109937291678436</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -4780,13 +4780,13 @@
         </is>
       </c>
       <c r="B191" s="17" t="n">
-        <v>0.3741947485548535</v>
+        <v>0.3731769583128968</v>
       </c>
       <c r="C191" s="17" t="n">
-        <v>0.3611591486898947</v>
+        <v>0.3619670392329837</v>
       </c>
       <c r="D191" s="17" t="n">
-        <v>0.2646461027552517</v>
+        <v>0.2648560024541195</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -4796,13 +4796,13 @@
         </is>
       </c>
       <c r="B192" s="17" t="n">
-        <v>0.3639303865701528</v>
+        <v>0.3651290070367477</v>
       </c>
       <c r="C192" s="17" t="n">
-        <v>0.225319574926844</v>
+        <v>0.224394057857701</v>
       </c>
       <c r="D192" s="17" t="n">
-        <v>0.4107500385030032</v>
+        <v>0.4104769351055512</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -4952,16 +4952,16 @@
         </is>
       </c>
       <c r="B203" s="17" t="n">
-        <v>4.699168514935588</v>
+        <v>4.713838828710869</v>
       </c>
       <c r="C203" s="17" t="n">
-        <v>5.049679109055732</v>
+        <v>5.029758362099749</v>
       </c>
       <c r="D203" s="17" t="n">
-        <v>4.107298853286772</v>
+        <v>4.112897869301272</v>
       </c>
       <c r="E203" s="17" t="n">
-        <v>13.85614647727809</v>
+        <v>13.85649506011189</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -4971,16 +4971,16 @@
         </is>
       </c>
       <c r="B204" s="17" t="n">
-        <v>2.042255785572736</v>
+        <v>2.047152138297271</v>
       </c>
       <c r="C204" s="17" t="n">
-        <v>1.433584479998209</v>
+        <v>1.428138805717191</v>
       </c>
       <c r="D204" s="17" t="n">
-        <v>2.26134442491351</v>
+        <v>2.26046551042314</v>
       </c>
       <c r="E204" s="17" t="n">
-        <v>5.737184690484455</v>
+        <v>5.735756454437603</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="B205" s="17" t="n">
-        <v>7.962864249247283</v>
+        <v>7.941205672898445</v>
       </c>
       <c r="C205" s="17" t="n">
-        <v>7.764921696832736</v>
+        <v>7.78229134350915</v>
       </c>
       <c r="D205" s="17" t="n">
-        <v>4.970053809743627</v>
+        <v>4.973995726088365</v>
       </c>
       <c r="E205" s="17" t="n">
-        <v>20.69783975582364</v>
+        <v>20.69749274249596</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -5009,16 +5009,16 @@
         </is>
       </c>
       <c r="B206" s="17" t="n">
-        <v>4.803881102726017</v>
+        <v>4.81970289288507</v>
       </c>
       <c r="C206" s="17" t="n">
-        <v>3.197284768211916</v>
+        <v>3.184151681000778</v>
       </c>
       <c r="D206" s="17" t="n">
-        <v>5.512265516710303</v>
+        <v>5.508600469116497</v>
       </c>
       <c r="E206" s="17" t="n">
-        <v>13.51343138764824</v>
+        <v>13.51245504300234</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>20.69783975582364</v>
+        <v>20.69749274249596</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>13.85614647727809</v>
+        <v>13.85649506011189</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>13.51343138764824</v>
+        <v>13.51245504300234</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>5.737184690484455</v>
+        <v>5.735756454437603</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>20.69783975582364</v>
+        <v>20.69749274249596</v>
       </c>
       <c r="D20" s="17" t="n">
         <v>21.94117647058823</v>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>13.85614647727809</v>
+        <v>13.85649506011189</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>13.85614647727809</v>
+        <v>13.85649506011189</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>13.51343138764824</v>
+        <v>13.51245504300234</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>13.51343138764824</v>
+        <v>13.51245504300234</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>5.737184690484455</v>
+        <v>5.735756454437603</v>
       </c>
       <c r="D28" s="17" t="n">
-        <v>5.737184690484455</v>
+        <v>5.735756454437603</v>
       </c>
     </row>
   </sheetData>
